--- a/Docs/Version 3/Test List.xlsx
+++ b/Docs/Version 3/Test List.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Delphi\Delphi13\Compo\FMXCompo\AiMaker\Docs\Version 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58DACAD6-537A-4A45-AA9C-A9CE2D421D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EC1B68-624A-4BC5-967E-4FC90E17EA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{C43F320B-4919-4C45-8A4A-589F1BA9D3EA}"/>
+    <workbookView xWindow="30330" yWindow="120" windowWidth="21120" windowHeight="20655" activeTab="1" xr2:uid="{C43F320B-4919-4C45-8A4A-589F1BA9D3EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja4" sheetId="4" r:id="rId2"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId3"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="76">
   <si>
     <t>Chat</t>
   </si>
@@ -219,6 +222,54 @@
   </si>
   <si>
     <t>Not updated yet</t>
+  </si>
+  <si>
+    <t>gemini-3-pro-preview</t>
+  </si>
+  <si>
+    <t>gemini-3-pro-image-preview</t>
+  </si>
+  <si>
+    <t>gemini-2.5-pro-preview-tts</t>
+  </si>
+  <si>
+    <t>veo-3.1-generate-preview</t>
+  </si>
+  <si>
+    <t>deep-research-pro-preview-12-2025</t>
+  </si>
+  <si>
+    <t>Robot view</t>
+  </si>
+  <si>
+    <t>gemini-robotics-er-1.5-preview</t>
+  </si>
+  <si>
+    <t>gemini-2.5-computer-use-preview-10-2025</t>
+  </si>
+  <si>
+    <t>Modelo Recomendado</t>
+  </si>
+  <si>
+    <t>Modelo</t>
+  </si>
+  <si>
+    <t>text-embedding-004</t>
+  </si>
+  <si>
+    <t>modelos que soportan estas caracteristicas</t>
+  </si>
+  <si>
+    <t>gpt-oss:20b</t>
+  </si>
+  <si>
+    <t>qwen3-vl:4b, llava:latest,deepseek-ocr:latest</t>
+  </si>
+  <si>
+    <t>gpt-5.2,gpt-5.2-2025-12-11,gpt-5.2-chat.latest,gpt-5.2-pro,gpt-5.2-pro-2025-12-11</t>
+  </si>
+  <si>
+    <t>gpt-5.2,gpt-5.2-2025-12-11,gpt-5.2-chat-latest,gpt-5.2-pro,gpt-5.2-pro-2025-12-11</t>
   </si>
 </sst>
 </file>
@@ -284,7 +335,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -333,11 +384,224 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -350,12 +614,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -363,6 +621,45 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -715,55 +1012,55 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="AA2" s="16" t="s">
+      <c r="AA2" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
     </row>
     <row r="3" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="G3" s="14" t="s">
+      <c r="D3" s="15"/>
+      <c r="G3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="J3" s="14" t="s">
+      <c r="H3" s="15"/>
+      <c r="J3" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="M3" s="14" t="s">
+      <c r="K3" s="15"/>
+      <c r="M3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="14"/>
-      <c r="P3" s="14" t="s">
+      <c r="N3" s="15"/>
+      <c r="P3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="14"/>
-      <c r="S3" s="14" t="s">
+      <c r="Q3" s="15"/>
+      <c r="S3" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="T3" s="14"/>
-      <c r="V3" s="14" t="s">
+      <c r="T3" s="15"/>
+      <c r="V3" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14" t="s">
+      <c r="W3" s="15"/>
+      <c r="X3" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="Y3" s="14"/>
-      <c r="AA3" s="14" t="s">
+      <c r="Y3" s="15"/>
+      <c r="AA3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="AB3" s="14"/>
-      <c r="AD3" s="14" t="s">
+      <c r="AB3" s="15"/>
+      <c r="AD3" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="AE3" s="14"/>
+      <c r="AE3" s="15"/>
     </row>
     <row r="4" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C4" s="3" t="s">
@@ -828,26 +1125,26 @@
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="C5" s="12"/>
-      <c r="D5" s="13"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="13"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="13"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="13"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="13"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="13"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="13"/>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="13"/>
-      <c r="AD5" s="12"/>
-      <c r="AE5" s="13"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="17"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="17"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="17"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="17"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="17"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="17"/>
+      <c r="AD5" s="16"/>
+      <c r="AE5" s="17"/>
     </row>
     <row r="6" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -1466,8 +1763,12 @@
       <c r="H18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="J18" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="M18" s="7" t="s">
         <v>23</v>
       </c>
@@ -1947,7 +2248,7 @@
       <c r="C27" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="13" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="6" t="s">
@@ -2885,6 +3186,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="AA5:AB5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="AD5:AE5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="P5:Q5"/>
     <mergeCell ref="AA2:AE2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="G3:H3"/>
@@ -2896,18 +3207,3360 @@
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="V3:W3"/>
     <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="X5:Y5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8707132B-5F81-49A8-B5E5-9B0AE3CFF390}">
+  <dimension ref="A1:I240"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="28"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="23"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="25"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="30"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="29"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="32"/>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="32"/>
+      <c r="B8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="29"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="32"/>
+      <c r="B10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="32"/>
+      <c r="B11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="32"/>
+      <c r="B12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="32"/>
+      <c r="B13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="32"/>
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="29"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="32"/>
+      <c r="B16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="32"/>
+      <c r="B17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="32"/>
+      <c r="B18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="32"/>
+      <c r="B19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="32"/>
+      <c r="B20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="29"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="32"/>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="32"/>
+      <c r="B23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="32"/>
+      <c r="B24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="32"/>
+      <c r="B25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="32"/>
+      <c r="B26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="32"/>
+      <c r="B27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="32"/>
+      <c r="B28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="39"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="21"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="15"/>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="23"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="25"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="32"/>
+      <c r="B36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="32"/>
+      <c r="B37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="32"/>
+      <c r="B38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="32"/>
+      <c r="B40" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="32"/>
+      <c r="B41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="32"/>
+      <c r="B42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="32"/>
+      <c r="B43" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="32"/>
+      <c r="B44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="32"/>
+      <c r="B46" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="32"/>
+      <c r="B47" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="32"/>
+      <c r="B48" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="32"/>
+      <c r="B49" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="32"/>
+      <c r="B50" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="32"/>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="32"/>
+      <c r="B53" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="32"/>
+      <c r="B54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="32"/>
+      <c r="B55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="32"/>
+      <c r="B56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="32"/>
+      <c r="B57" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="32"/>
+      <c r="B58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B59" s="38"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+    </row>
+    <row r="61" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="21"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" s="15"/>
+    </row>
+    <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="23"/>
+      <c r="B63" s="24"/>
+      <c r="C63" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="25"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="17"/>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="20"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="32"/>
+      <c r="B66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="32"/>
+      <c r="B67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="32"/>
+      <c r="B68" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="32"/>
+      <c r="B70" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="32"/>
+      <c r="B71" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="32"/>
+      <c r="B72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="32"/>
+      <c r="B73" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="32"/>
+      <c r="B74" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="32"/>
+      <c r="B76" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="32"/>
+      <c r="B77" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="32"/>
+      <c r="B78" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="32"/>
+      <c r="B79" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="32"/>
+      <c r="B80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="32"/>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82" s="8"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="32"/>
+      <c r="B83" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="32"/>
+      <c r="B84" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="32"/>
+      <c r="B85" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="32"/>
+      <c r="B86" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="32"/>
+      <c r="B87" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="32"/>
+      <c r="B88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B89" s="38"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+    </row>
+    <row r="91" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="21"/>
+      <c r="B92" s="22"/>
+      <c r="C92" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D92" s="15"/>
+    </row>
+    <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="23"/>
+      <c r="B93" s="24"/>
+      <c r="C93" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="25"/>
+      <c r="B94" s="26"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A95" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B95" s="20"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="32"/>
+      <c r="B96" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="32"/>
+      <c r="B97" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="32"/>
+      <c r="B98" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B99" s="4"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="32"/>
+      <c r="B100" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="32"/>
+      <c r="B101" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="32"/>
+      <c r="B102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="32"/>
+      <c r="B103" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="32"/>
+      <c r="B104" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B105" s="4"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="32"/>
+      <c r="B106" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="32"/>
+      <c r="B107" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="32"/>
+      <c r="B108" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="32"/>
+      <c r="B109" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="32"/>
+      <c r="B110" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A111" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="32"/>
+      <c r="B112" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E112" s="8"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="32"/>
+      <c r="B113" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="32"/>
+      <c r="B114" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="32"/>
+      <c r="B115" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="32"/>
+      <c r="B116" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="32"/>
+      <c r="B117" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="32"/>
+      <c r="B118" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B119" s="38"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+    </row>
+    <row r="121" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="122" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A122" s="21"/>
+      <c r="B122" s="22"/>
+      <c r="C122" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D122" s="15"/>
+    </row>
+    <row r="123" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A123" s="23"/>
+      <c r="B123" s="24"/>
+      <c r="C123" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="25"/>
+      <c r="B124" s="26"/>
+      <c r="C124" s="16"/>
+      <c r="D124" s="17"/>
+    </row>
+    <row r="125" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A125" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B125" s="20"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="32"/>
+      <c r="B126" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="32"/>
+      <c r="B127" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="32"/>
+      <c r="B128" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A129" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B129" s="4"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="32"/>
+      <c r="B130" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="32"/>
+      <c r="B131" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="32"/>
+      <c r="B132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="32"/>
+      <c r="B133" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="32"/>
+      <c r="B134" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A135" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B135" s="4"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="32"/>
+      <c r="B136" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="32"/>
+      <c r="B137" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="32"/>
+      <c r="B138" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="32"/>
+      <c r="B139" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="32"/>
+      <c r="B140" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A141" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="32"/>
+      <c r="B142" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E142" s="8"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="32"/>
+      <c r="B143" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="32"/>
+      <c r="B144" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="32"/>
+      <c r="B145" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="32"/>
+      <c r="B146" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="32"/>
+      <c r="B147" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="32"/>
+      <c r="B148" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B149" s="38"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+    </row>
+    <row r="151" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="152" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A152" s="21"/>
+      <c r="B152" s="22"/>
+      <c r="C152" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D152" s="15"/>
+    </row>
+    <row r="153" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A153" s="23"/>
+      <c r="B153" s="24"/>
+      <c r="C153" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="25"/>
+      <c r="B154" s="26"/>
+      <c r="C154" s="16"/>
+      <c r="D154" s="17"/>
+    </row>
+    <row r="155" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A155" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B155" s="20"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" s="32"/>
+      <c r="B156" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" s="32"/>
+      <c r="B157" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" s="32"/>
+      <c r="B158" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A159" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B159" s="4"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" s="32"/>
+      <c r="B160" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="32"/>
+      <c r="B161" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="32"/>
+      <c r="B162" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="32"/>
+      <c r="B163" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="32"/>
+      <c r="B164" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A165" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B165" s="4"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="32"/>
+      <c r="B166" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="32"/>
+      <c r="B167" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D167" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="32"/>
+      <c r="B168" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="32"/>
+      <c r="B169" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="32"/>
+      <c r="B170" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A171" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B171" s="3"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="32"/>
+      <c r="B172" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E172" s="8"/>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="32"/>
+      <c r="B173" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="32"/>
+      <c r="B174" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="32"/>
+      <c r="B175" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="32"/>
+      <c r="B176" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" s="32"/>
+      <c r="B177" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" s="32"/>
+      <c r="B178" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B179" s="38"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+    </row>
+    <row r="181" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="182" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A182" s="21"/>
+      <c r="B182" s="22"/>
+      <c r="C182" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D182" s="15"/>
+    </row>
+    <row r="183" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A183" s="23"/>
+      <c r="B183" s="24"/>
+      <c r="C183" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="25"/>
+      <c r="B184" s="26"/>
+      <c r="C184" s="16"/>
+      <c r="D184" s="17"/>
+    </row>
+    <row r="185" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A185" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B185" s="20"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" s="32"/>
+      <c r="B186" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" s="32"/>
+      <c r="B187" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" s="32"/>
+      <c r="B188" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A189" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B189" s="4"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3"/>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" s="32"/>
+      <c r="B190" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" s="32"/>
+      <c r="B191" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D191" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" s="32"/>
+      <c r="B192" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" s="32"/>
+      <c r="B193" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D193" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" s="32"/>
+      <c r="B194" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A195" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B195" s="4"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3"/>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" s="32"/>
+      <c r="B196" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D196" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="32"/>
+      <c r="B197" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C197" s="7"/>
+      <c r="D197" s="7"/>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="32"/>
+      <c r="B198" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D198" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="32"/>
+      <c r="B199" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="32"/>
+      <c r="B200" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D200" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A201" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B201" s="3"/>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3"/>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" s="32"/>
+      <c r="B202" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203" s="32"/>
+      <c r="B203" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D203" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204" s="32"/>
+      <c r="B204" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D204" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" s="32"/>
+      <c r="B205" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" s="32"/>
+      <c r="B206" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D206" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207" s="32"/>
+      <c r="B207" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C207" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D207" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" s="32"/>
+      <c r="B208" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C208" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D208" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B209" s="38"/>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
+    </row>
+    <row r="212" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="213" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A213" s="21"/>
+      <c r="B213" s="22"/>
+      <c r="C213" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D213" s="15"/>
+    </row>
+    <row r="214" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A214" s="23"/>
+      <c r="B214" s="24"/>
+      <c r="C214" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="25"/>
+      <c r="B215" s="26"/>
+      <c r="C215" s="16"/>
+      <c r="D215" s="17"/>
+    </row>
+    <row r="216" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A216" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B216" s="20"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="3"/>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217" s="32"/>
+      <c r="B217" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218" s="32"/>
+      <c r="B218" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219" s="32"/>
+      <c r="B219" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C219" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D219" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A220" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B220" s="4"/>
+      <c r="C220" s="3"/>
+      <c r="D220" s="3"/>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221" s="32"/>
+      <c r="B221" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C221" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D221" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222" s="32"/>
+      <c r="B222" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D222" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223" s="32"/>
+      <c r="B223" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D223" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224" s="32"/>
+      <c r="B224" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C224" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D224" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225" s="32"/>
+      <c r="B225" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A226" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B226" s="4"/>
+      <c r="C226" s="3"/>
+      <c r="D226" s="3"/>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227" s="32"/>
+      <c r="B227" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D227" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228" s="32"/>
+      <c r="B228" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C228" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D228" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229" s="32"/>
+      <c r="B229" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C229" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D229" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230" s="32"/>
+      <c r="B230" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C230" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D230" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231" s="32"/>
+      <c r="B231" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C231" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D231" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A232" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B232" s="3"/>
+      <c r="C232" s="3"/>
+      <c r="D232" s="3"/>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233" s="32"/>
+      <c r="B233" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D233" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234" s="32"/>
+      <c r="B234" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C234" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D234" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235" s="32"/>
+      <c r="B235" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C235" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D235" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236" s="32"/>
+      <c r="B236" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C236" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D236" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237" s="32"/>
+      <c r="B237" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C237" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D237" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238" s="32"/>
+      <c r="B238" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C238" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D238" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239" s="32"/>
+      <c r="B239" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C239" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D239" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B240" s="38"/>
+      <c r="C240" s="3"/>
+      <c r="D240" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="C213:D213"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="C215:D215"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C152:D152"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F610CDD-1195-45A0-A080-245F0725A39D}">
+  <dimension ref="A3:G36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="1.5703125" customWidth="1"/>
+    <col min="6" max="6" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D3" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="15"/>
+      <c r="F3" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23" s="8"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B36" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F892C512-650C-4137-814F-F3B34711F2C0}">
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="15"/>
+      <c r="E1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="4"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="4"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="4"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="3"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>